--- a/output/pdf_financials_xlsx/TVI.xlsx
+++ b/output/pdf_financials_xlsx/TVI.xlsx
@@ -4953,28 +4953,28 @@
         <v>0</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0</v>
+        <v>-3.293298</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0</v>
+        <v>-1.179823</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>-2.533601</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0</v>
+        <v>-4.111679</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0</v>
+        <v>-5.242126</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0</v>
+        <v>-5.766447</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>0</v>
+        <v>-4.437551</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>0</v>
+        <v>-5.934998</v>
       </c>
     </row>
     <row r="92">
@@ -9147,7 +9147,11 @@
           <t>Translation reserves</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -10403,7 +10407,11 @@
           <t>Translation reserves</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TVI.xlsx
+++ b/output/pdf_financials_xlsx/TVI.xlsx
@@ -902,28 +902,28 @@
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0</v>
+        <v>4.787674</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0</v>
+        <v>6.267763</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0</v>
+        <v>1.557537</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0</v>
+        <v>1.451054</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0</v>
+        <v>1.599998</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0</v>
+        <v>2.560161</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0</v>
+        <v>1.769091</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0</v>
+        <v>1.219491</v>
       </c>
     </row>
     <row r="11">
@@ -1014,10 +1014,10 @@
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.106147</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.269687</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-6.927744</v>
+        <v>-7.033891</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-5.378228</v>
+        <v>-5.647915</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>1.293081</v>
@@ -2016,10 +2016,10 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-6.927744</v>
+        <v>-7.033891</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-5.378228</v>
+        <v>-5.647915</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>1.293081</v>
@@ -2290,7 +2290,7 @@
         <v>0.18431</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.209189</v>
       </c>
     </row>
     <row r="35">
@@ -2382,7 +2382,7 @@
         <v>0.18431</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.209189</v>
       </c>
     </row>
     <row r="37">
@@ -2934,7 +2934,7 @@
         <v>0.00485</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.236816</v>
+        <v>0.027627</v>
       </c>
     </row>
     <row r="49">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -25851,7 +25851,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -31063,7 +31063,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -31146,7 +31146,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
